--- a/docs/OrganizationIntranet-ToDo.xlsx
+++ b/docs/OrganizationIntranet-ToDo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="321">
   <si>
     <t>فاز</t>
   </si>
@@ -487,7 +487,7 @@
     <t>تبدیل مجوز صفحات Admin از Roles=ADMIN به Permission-based با Seed مجوزهای پایه</t>
   </si>
   <si>
-    <t>طبق CLAUDE.md؛ با آزمون جلوگیری از قفل‌شدن مدیر و Logout/Login بعد از Seed</t>
+    <t>migration 008_AdminPermissions روی بانک توسعه اعمال و verify شد (backup OrganizationIntranet_before_008_20261021_1628.bak). ۱۲ مجوز پنل در shared/Contracts/AdminPermissions.cs؛ API مجوز را زنده از بانک می‌خواند، UI هر ۵ دقیقه Claimها را تازه می‌کند (Logout/Login لازم نیست). جلوگیری از قفل‌شدن: نقش ADMIN و مجوزهای سیستمی غیرفعال نمی‌شوند و آخرین مدیر فعال حذف نمی‌شود. docs/admin-permissions.md، AdminPermissionTests.</t>
   </si>
   <si>
     <t>P4-10</t>
@@ -598,7 +598,7 @@
     <t>افزودن تست برای هر فاز، به‌ویژه مرز عمومی/خصوصی (الان ۵۷ تست قبول است)</t>
   </si>
   <si>
-    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۴۳ تست قبول + ۹ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
+    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۴۸ تست قبول + ۱۰ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
   </si>
   <si>
     <t>P6-05</t>
@@ -652,19 +652,28 @@
     <t>نمایش QR code در صفحه‌ی Google Authenticator (کتابخانه‌ی آفلاین)</t>
   </si>
   <si>
-    <t>API نشانی provisioning را برمی‌گرداند؛ الان کلید دستی وارد می‌شود.</t>
+    <t>کاربر فعلاً به Google Authenticator نیاز ندارد و هنوز تصمیم نگرفته که در سامانه بماند.</t>
   </si>
   <si>
     <t>P6-11</t>
   </si>
   <si>
+    <t>فعال‌سازی «ورود با کد ملی و پیامک» برای هر کاربر توسط مدیر</t>
+  </si>
+  <si>
+    <t>هنوز بحث نشده؛ شاید همان ورود با نام کاربری و رمز کافی باشد. پیشنهاد اولیه: مدیر در کارتابل برای هر کاربر فعال کند.</t>
+  </si>
+  <si>
+    <t>P6-12</t>
+  </si>
+  <si>
     <t>صفحه‌های خطای ۴۰۴ و ۵۰۰ هم‌خوان با تم هر دو پرتال</t>
   </si>
   <si>
     <t>الان صفحه‌ی Error پیش‌فرض است.</t>
   </si>
   <si>
-    <t>P6-12</t>
+    <t>P6-13</t>
   </si>
   <si>
     <t>لاگ ساختاریافته‌ی عملیات (چه کسی، چه زمانی، چه چیزی) و جدول Audit قابل جستجو در پنل مدیریت</t>
@@ -673,7 +682,7 @@
     <t>تکمیل P4-08؛ الان Audit فقط در لاگ برنامه نوشته می‌شود.</t>
   </si>
   <si>
-    <t>P6-13</t>
+    <t>P6-14</t>
   </si>
   <si>
     <t>health check برای API و پایش اتصال بانک/پیامک/LDAP</t>
@@ -880,13 +889,13 @@
     <t>مجوزدهی Permission-based در پنل</t>
   </si>
   <si>
-    <t>زیرساخت آماده است؛ صفحه‌ها هنوز Roles=ADMIN (P4-09)</t>
+    <t>هر صفحه و endpoint مجوز خودش را دارد؛ منو و دکمه‌ها هم بر اساس مجوز (P4-09، migration 008)</t>
   </si>
   <si>
     <t>دیتابیس: migrationها</t>
   </si>
   <si>
-    <t>بانک توسعه 001 تا 007 را دارد؛ فایل‌های 003_ApplicationCatalog در مخزن نیست (P0-10)</t>
+    <t>بانک توسعه 001 تا 008 را دارد؛ فایل‌های 003_ApplicationCatalog در مخزن نیست (P0-10)</t>
   </si>
   <si>
     <t>داده‌ی آزمایشی در بانک توسعه</t>
@@ -946,16 +955,28 @@
     <t>دید بازدیدکننده‌ی ناشناس</t>
   </si>
   <si>
+    <t>بعداً در یک فهرست کلی مشخص می‌شود؛ فعلاً به همین صورت آزمایشی بماند.</t>
+  </si>
+  <si>
     <t>فایل فرم‌ها و پیوست مطالب کجا ذخیره شود (دیسک سرور یا بانک) و سقف حجم؟</t>
   </si>
   <si>
+    <t>روی دیسک، در پوشه‌ی Downloads درایو C؛ مسیر در تنظیمات قابل تغییر باشد (برای استقرار روی سرور بازبینی شود).</t>
+  </si>
+  <si>
     <t>ورود با کد ملی و پیامک یک‌عاملی است؛ برای چه کاربرانی فعال شود؟</t>
   </si>
   <si>
     <t>امنیت ورود</t>
   </si>
   <si>
+    <t>به تعویق افتاد؛ هنوز بحث نشده و شاید همان ورود با نام کاربری و رمز کافی باشد.</t>
+  </si>
+  <si>
     <t>مطالب قدیمی حذف شوند یا بایگانی؟ مدت نگه‌داری؟</t>
+  </si>
+  <si>
+    <t>نیاز به بحث دارد؛ فعلاً سراغ آن نمی‌رویم.</t>
   </si>
 </sst>
 </file>
@@ -1463,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2786,7 +2807,7 @@
         <v>35</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>16</v>
@@ -3326,7 +3347,7 @@
         <v>69</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>16</v>
@@ -3350,13 +3371,13 @@
         <v>214</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>16</v>
@@ -3380,7 +3401,7 @@
         <v>217</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>35</v>
@@ -3389,7 +3410,7 @@
         <v>51</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>16</v>
@@ -3410,7 +3431,7 @@
         <v>220</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>35</v>
@@ -3419,7 +3440,7 @@
         <v>51</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>16</v>
@@ -3431,22 +3452,22 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="D66" s="3" t="s">
-        <v>225</v>
+        <v>13</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>16</v>
@@ -3456,21 +3477,21 @@
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>14</v>
@@ -3486,21 +3507,21 @@
       </c>
       <c r="I67" s="6"/>
       <c r="J67" s="2" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>14</v>
@@ -3521,16 +3542,16 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>14</v>
@@ -3551,16 +3572,16 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>14</v>
@@ -3581,16 +3602,16 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>14</v>
@@ -3611,16 +3632,16 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>14</v>
@@ -3636,12 +3657,12 @@
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="2" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>240</v>
@@ -3650,7 +3671,7 @@
         <v>241</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>14</v>
@@ -3666,21 +3687,21 @@
       </c>
       <c r="I73" s="6"/>
       <c r="J73" s="2" t="s">
-        <v>16</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>14</v>
@@ -3701,22 +3722,22 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>16</v>
@@ -3731,16 +3752,16 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>35</v>
@@ -3756,12 +3777,12 @@
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="2" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>249</v>
@@ -3770,7 +3791,7 @@
         <v>250</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>35</v>
@@ -3786,27 +3807,57 @@
       </c>
       <c r="I77" s="6"/>
       <c r="J77" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
         <v>251</v>
       </c>
     </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="6"/>
+      <c r="J78" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="8" t="s">
-        <v>252</v>
+      <c r="A80" s="7" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J77"/>
-  <conditionalFormatting sqref="F2:F77">
+  <autoFilter ref="A1:J78"/>
+  <conditionalFormatting sqref="F2:F78">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"انجام شد"</formula>
     </cfRule>
@@ -3820,22 +3871,22 @@
       <formula>"به‌تعویق"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E77">
+  <conditionalFormatting sqref="E2:E78">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"بالا"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="E10:E77">
+    <dataValidation type="list" sqref="E10:E78">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E77">
+    <dataValidation type="list" sqref="E2:E78">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F10:F77">
+    <dataValidation type="list" sqref="F10:F78">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F77">
+    <dataValidation type="list" sqref="F2:F78">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3863,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
@@ -3872,7 +3923,7 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
@@ -3881,7 +3932,7 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3889,27 +3940,27 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A2)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A2)</f>
         <v>13</v>
       </c>
       <c r="C2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A2,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>7</v>
       </c>
       <c r="D2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A2,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A2,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A2,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A2,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
         <v>3</v>
       </c>
       <c r="H2" s="9">
@@ -3922,27 +3973,27 @@
         <v>62</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A3)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A3)</f>
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A3,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A3,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A3,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A3,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A3,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H3" s="9">
@@ -3955,27 +4006,27 @@
         <v>76</v>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A4)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A4)</f>
         <v>8</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A4,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>7</v>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A4,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A4,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A4,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A4,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H4" s="9">
@@ -3988,27 +4039,27 @@
         <v>104</v>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A5)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A5)</f>
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A5,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A5,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A5,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A5,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A5,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
         <v>8</v>
       </c>
       <c r="H5" s="9">
@@ -4021,32 +4072,32 @@
         <v>132</v>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A6)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A6)</f>
         <v>11</v>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A6,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <v>2</v>
+      </c>
+      <c r="E6" s="3">
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
-      <c r="D6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A6,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
-        <v>2</v>
-      </c>
-      <c r="E6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A6,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+      <c r="F6" s="3">
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>0</v>
       </c>
-      <c r="F6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A6,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
-        <v>0</v>
-      </c>
       <c r="G6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A6,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
-        <v>9</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <v>8</v>
       </c>
       <c r="H6" s="9">
         <f>IFERROR(C6/B6,0)</f>
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -4054,27 +4105,27 @@
         <v>163</v>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A7)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A7)</f>
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A7,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A7,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A7,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A7,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A7,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
         <v>5</v>
       </c>
       <c r="H7" s="9">
@@ -4087,60 +4138,60 @@
         <v>182</v>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A8)</f>
-        <v>13</v>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A8)</f>
+        <v>14</v>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A8,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>5</v>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A8,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A8,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A8,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
-        <v>0</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <v>2</v>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A8,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
-        <v>5</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <v>4</v>
       </c>
       <c r="H8" s="9">
         <f>IFERROR(C8/B8,0)</f>
-        <v>0.38461538461538464</v>
+        <v>0.35714285714285715</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$77,A9)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A9)</f>
         <v>12</v>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A9,'لیست کارها'!$F$2:$F$77,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
         <v>9</v>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A9,'لیست کارها'!$F$2:$F$77,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A9,'لیست کارها'!$F$2:$F$77,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A9,'لیست کارها'!$F$2:$F$77,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$77,A9,'لیست کارها'!$F$2:$F$77,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
         <v>3</v>
       </c>
       <c r="H9" s="9">
@@ -4150,15 +4201,15 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B10" s="11">
         <f>SUM(B2:B9)</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D2:D9)</f>
@@ -4170,20 +4221,20 @@
       </c>
       <c r="F10" s="11">
         <f>SUM(F2:F9)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="11">
         <f>SUM(G2:G9)</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H10" s="12">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0.42105263157894735</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4204,65 +4255,65 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>138</v>
@@ -4270,112 +4321,112 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4407,101 +4458,101 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>16</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>16</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/docs/OrganizationIntranet-ToDo.xlsx
+++ b/docs/OrganizationIntranet-ToDo.xlsx
@@ -451,7 +451,7 @@
     <t>نقش‌ها: ویرایش نام/کد و جلوگیری از حذف نقش دارای کاربر یا Permission</t>
   </si>
   <si>
-    <t>الان فقط ساخت و toggle دارد</t>
+    <t>صفحه‌ی Roles/Edit: ویرایش نام و کد (کد یکتا و با قالب معتبر؛ کد ADMIN و EXPERT ثابت)، اعضا و مجوزهای نقش، شمار کاربران/مجوزها در فهرست، حذف فقط برای نقش استفاده‌نشده. RoleManagementTests.</t>
   </si>
   <si>
     <t>P4-06</t>
@@ -598,7 +598,7 @@
     <t>افزودن تست برای هر فاز، به‌ویژه مرز عمومی/خصوصی (الان ۵۷ تست قبول است)</t>
   </si>
   <si>
-    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۴۸ تست قبول + ۱۰ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
+    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۵۸ تست قبول + ۱۰ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
   </si>
   <si>
     <t>P6-05</t>
@@ -877,7 +877,7 @@
     <t>Admin: نقش‌ها</t>
   </si>
   <si>
-    <t>فقط ساخت و toggle؛ ویرایش و حذف ندارد</t>
+    <t>ساخت، ویرایش نام/کد، جزئیات اعضا و مجوزها، شمارها، فعال/غیرفعال، حذف نقش استفاده‌نشده</t>
   </si>
   <si>
     <t>Admin: سامانه‌ها</t>
@@ -2687,7 +2687,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>16</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="C6" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
@@ -4093,11 +4093,11 @@
       </c>
       <c r="G6" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="9">
         <f>IFERROR(C6/B6,0)</f>
-        <v>0.09090909090909091</v>
+        <v>0.18181818181818182</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D2:D9)</f>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="G10" s="11">
         <f>SUM(G2:G9)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="12">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0.42857142857142855</v>
+        <v>0.44155844155844154</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -4379,7 +4379,7 @@
         <v>286</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>287</v>

--- a/docs/OrganizationIntranet-ToDo.xlsx
+++ b/docs/OrganizationIntranet-ToDo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="322">
   <si>
     <t>فاز</t>
   </si>
@@ -496,7 +496,7 @@
     <t>صفحه‌ی اعلان‌ها: صفحه‌بندی سمت سرور (الان ۵۰ اعلان آخر) و فیلتر تاریخ</t>
   </si>
   <si>
-    <t>API فعلی فقط ۵۰ مورد آخر را برمی‌گرداند.</t>
+    <t>api/portal/notifications/page: UNION ALL دو منبع، صفحه‌بندی ۲۰تایی، تب با شمار، فیلتر منبع و بازه (۲۴ ساعت/۷/۳۰/۹۰ روز)؛ شمار زنگ هدر هم دقیق شد. NotificationCenterTests + آزمون SQL Server.</t>
   </si>
   <si>
     <t>P4-11</t>
@@ -598,7 +598,7 @@
     <t>افزودن تست برای هر فاز، به‌ویژه مرز عمومی/خصوصی (الان ۵۷ تست قبول است)</t>
   </si>
   <si>
-    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۵۸ تست قبول + ۱۰ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
+    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۶۵ تست قبول + ۱۱ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
   </si>
   <si>
     <t>P6-05</t>
@@ -760,7 +760,10 @@
     <t>P7-10</t>
   </si>
   <si>
-    <t>بازطراحی «کارتابل نظارت» در صفحه‌ی اصلی Portal (هنوز ظاهر ساده دارد)</t>
+    <t>بازطراحی «کارتابل نظارت»: صفحه‌ی /Supervision با تب وضعیت، فیلتر سامانه و صفحه‌بندی؛ کارت خلاصه در صفحه‌ی اصلی و منوی حساب برای ناظر</t>
+  </si>
+  <si>
+    <t>فیلتر وضعیت «درخواست‌های من» هم سمت سرور شد</t>
   </si>
   <si>
     <t>P7-11</t>
@@ -2837,7 +2840,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>16</v>
@@ -3764,10 +3767,10 @@
         <v>228</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>16</v>
@@ -3777,7 +3780,7 @@
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="2" t="s">
-        <v>16</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -3785,10 +3788,10 @@
         <v>225</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>228</v>
@@ -3807,7 +3810,7 @@
       </c>
       <c r="I77" s="6"/>
       <c r="J77" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -3815,10 +3818,10 @@
         <v>225</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>228</v>
@@ -3842,17 +3845,17 @@
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3914,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
@@ -3923,7 +3926,7 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
@@ -3932,7 +3935,7 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4077,7 +4080,7 @@
       </c>
       <c r="C6" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
@@ -4093,11 +4096,11 @@
       </c>
       <c r="G6" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" s="9">
         <f>IFERROR(C6/B6,0)</f>
-        <v>0.18181818181818182</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -4176,7 +4179,7 @@
       </c>
       <c r="C9" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
@@ -4192,16 +4195,16 @@
       </c>
       <c r="G9" s="3">
         <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B10" s="11">
         <f>SUM(B2:B9)</f>
@@ -4209,7 +4212,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D2:D9)</f>
@@ -4225,16 +4228,16 @@
       </c>
       <c r="G10" s="11">
         <f>SUM(G2:G9)</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H10" s="12">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0.44155844155844154</v>
+        <v>0.4675324675324675</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4255,65 +4258,65 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>138</v>
@@ -4321,112 +4324,112 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -4458,101 +4461,101 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>

--- a/docs/OrganizationIntranet-ToDo.xlsx
+++ b/docs/OrganizationIntranet-ToDo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="325">
   <si>
     <t>فاز</t>
   </si>
@@ -169,33 +169,42 @@
     <t>دیتابیس</t>
   </si>
   <si>
+    <t>003 up/down/verify از روی دیتابیس مرجع بازسازی شد؛ 004 به database/migrations منتقل شد؛ خط پایه‌ی نصب تازه 000_Baseline.install.sql (حالت بعد از 002، برابر با docs/database-catalog.md). FreshInstallTests روی LocalDB: خط پایه + 003..008 = دیتابیس مرجع (۲۷۳ از ۲۷۳ ردیف ساختار)، بازگشت و نصب دوباره.</t>
+  </si>
+  <si>
+    <t>P0-11</t>
+  </si>
+  <si>
+    <t>اعمال migrationهای 006_NationalIdLogin و 007_PublicationImages روی بانک توسعه</t>
+  </si>
+  <si>
+    <t>با backup COPY_ONLY+CHECKSUM (OrganizationIntranet_before_006_007_20261021_1516.bak)، verify هر دو موفق؛ ۹ تست بانک واقعی قبول. تاریخچه‌ی بانک: 001 تا 007.</t>
+  </si>
+  <si>
+    <t>P0-12</t>
+  </si>
+  <si>
+    <t>پاک‌سازی داده‌ی آزمایشی پیش از بهره‌برداری</t>
+  </si>
+  <si>
     <t>انجام نشده</t>
   </si>
   <si>
-    <t>دیتابیس فعلی آن را دارد ولی فایل‌هایش در مخزن نیست؛ masoud آن‌ها را نداشت. راه: ساخت از روی دیتابیس (Generate Scripts / تفاوت با 002) و بازبینی. 004 در tools/sql هست.</t>
-  </si>
-  <si>
-    <t>P0-11</t>
-  </si>
-  <si>
-    <t>اعمال migrationهای 006_NationalIdLogin و 007_PublicationImages روی بانک توسعه</t>
-  </si>
-  <si>
-    <t>با backup COPY_ONLY+CHECKSUM (OrganizationIntranet_before_006_007_20261021_1516.bak)، verify هر دو موفق؛ ۹ تست بانک واقعی قبول. تاریخچه‌ی بانک: 001 تا 007.</t>
-  </si>
-  <si>
-    <t>P0-12</t>
-  </si>
-  <si>
-    <t>پاک‌سازی داده‌ی آزمایشی پیش از بهره‌برداری</t>
-  </si>
-  <si>
     <t>برای تست اضافه شد: ۸ مطلب (+۱ پیش‌نویس)، سرویس اعلان روی سامانه‌های ۲ و ۵، اعلان‌ها و ۴ درخواست دسترسی. همه با عبارت «داده‌ی آزمایشی» در متن.</t>
   </si>
   <si>
     <t>P0-13</t>
   </si>
   <si>
+    <t>ابزار ساخت اولین مدیر برای نصب تازه (نام کاربری + رمز با PasswordHasher، بدون ثبت رمز در لاگ)</t>
+  </si>
+  <si>
+    <t>نصب تازه کاربری ندارد و verify 008 تا ساخت اولین مدیر خطا می‌دهد؛ database/migrations/README.md</t>
+  </si>
+  <si>
+    <t>P0-14</t>
+  </si>
+  <si>
     <t>merge شاخه‌ی ms به master پس از بازبینی</t>
   </si>
   <si>
@@ -598,7 +607,7 @@
     <t>افزودن تست برای هر فاز، به‌ویژه مرز عمومی/خصوصی (الان ۵۷ تست قبول است)</t>
   </si>
   <si>
-    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۶۵ تست قبول + ۱۱ تست بانک واقعی (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
+    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۶۶ تست قبول + ۱۲ تست بانک واقعی/نصب تازه (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
   </si>
   <si>
     <t>P6-05</t>
@@ -898,7 +907,7 @@
     <t>دیتابیس: migrationها</t>
   </si>
   <si>
-    <t>بانک توسعه 001 تا 008 را دارد؛ فایل‌های 003_ApplicationCatalog در مخزن نیست (P0-10)</t>
+    <t>همه‌ی فایل‌های 001 تا 008 در مخزن‌اند؛ نصب تازه با خط پایه + migrationها آزموده شد. ابزار اولین مدیر باقی است</t>
   </si>
   <si>
     <t>داده‌ی آزمایشی در بانک توسعه</t>
@@ -1487,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1820,7 +1829,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>16</v>
@@ -1830,7 +1839,7 @@
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1838,10 +1847,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>50</v>
@@ -1860,7 +1869,7 @@
       </c>
       <c r="I12" s="6"/>
       <c r="J12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1868,10 +1877,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>50</v>
@@ -1880,7 +1889,7 @@
         <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>16</v>
@@ -1904,13 +1913,13 @@
         <v>60</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>16</v>
@@ -1925,22 +1934,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>16</v>
@@ -1950,24 +1959,24 @@
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>15</v>
@@ -1980,24 +1989,24 @@
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>15</v>
@@ -2015,7 +2024,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>74</v>
@@ -2024,13 +2033,13 @@
         <v>75</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>16</v>
@@ -2040,12 +2049,12 @@
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>77</v>
@@ -2054,13 +2063,13 @@
         <v>78</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>16</v>
@@ -2070,12 +2079,12 @@
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="2" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>80</v>
@@ -2084,7 +2093,7 @@
         <v>81</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>14</v>
@@ -2093,28 +2102,28 @@
         <v>15</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>14</v>
@@ -2123,37 +2132,37 @@
         <v>15</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>16</v>
@@ -2165,7 +2174,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>91</v>
@@ -2174,16 +2183,16 @@
         <v>92</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>16</v>
@@ -2195,7 +2204,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>94</v>
@@ -2204,7 +2213,7 @@
         <v>95</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>14</v>
@@ -2213,37 +2222,37 @@
         <v>15</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>16</v>
@@ -2255,7 +2264,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>101</v>
@@ -2264,13 +2273,13 @@
         <v>102</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>16</v>
@@ -2285,22 +2294,22 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>16</v>
@@ -2310,12 +2319,12 @@
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>108</v>
@@ -2330,7 +2339,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>16</v>
@@ -2345,7 +2354,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>111</v>
@@ -2360,7 +2369,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>16</v>
@@ -2375,7 +2384,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>114</v>
@@ -2384,13 +2393,13 @@
         <v>115</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>16</v>
@@ -2400,72 +2409,72 @@
       </c>
       <c r="I30" s="6"/>
       <c r="J30" s="2" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I31" s="6"/>
       <c r="J31" s="2" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I32" s="6"/>
       <c r="J32" s="2" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>123</v>
@@ -2474,13 +2483,13 @@
         <v>124</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>125</v>
@@ -2495,7 +2504,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>126</v>
@@ -2504,28 +2513,28 @@
         <v>127</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="2" t="s">
-        <v>128</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>129</v>
@@ -2534,16 +2543,16 @@
         <v>130</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>16</v>
@@ -2555,37 +2564,37 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>136</v>
@@ -2594,28 +2603,28 @@
         <v>137</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I37" s="6"/>
       <c r="J37" s="2" t="s">
-        <v>16</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>139</v>
@@ -2624,16 +2633,16 @@
         <v>140</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>16</v>
@@ -2645,25 +2654,25 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>16</v>
@@ -2675,37 +2684,37 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="2" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>146</v>
@@ -2714,73 +2723,73 @@
         <v>147</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I41" s="6"/>
       <c r="J41" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I42" s="6"/>
       <c r="J42" s="2" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>16</v>
@@ -2790,12 +2799,12 @@
       </c>
       <c r="I43" s="6"/>
       <c r="J43" s="2" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>155</v>
@@ -2810,7 +2819,7 @@
         <v>35</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>16</v>
@@ -2825,7 +2834,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>158</v>
@@ -2834,7 +2843,7 @@
         <v>159</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>35</v>
@@ -2855,7 +2864,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>161</v>
@@ -2864,13 +2873,13 @@
         <v>162</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>16</v>
@@ -2880,12 +2889,12 @@
       </c>
       <c r="I46" s="6"/>
       <c r="J46" s="2" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>164</v>
@@ -2894,16 +2903,16 @@
         <v>165</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>16</v>
@@ -2915,7 +2924,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>167</v>
@@ -2924,16 +2933,16 @@
         <v>168</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>16</v>
@@ -2945,67 +2954,67 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="2" t="s">
-        <v>172</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="2" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>176</v>
@@ -3014,28 +3023,28 @@
         <v>177</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>178</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I51" s="6"/>
       <c r="J51" s="2" t="s">
-        <v>178</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>179</v>
@@ -3044,58 +3053,58 @@
         <v>180</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="2" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I53" s="6"/>
       <c r="J53" s="2" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>186</v>
@@ -3125,7 +3134,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>189</v>
@@ -3137,7 +3146,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>15</v>
@@ -3155,7 +3164,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>192</v>
@@ -3164,10 +3173,10 @@
         <v>193</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>15</v>
@@ -3185,7 +3194,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>195</v>
@@ -3194,13 +3203,13 @@
         <v>196</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>16</v>
@@ -3210,18 +3219,18 @@
       </c>
       <c r="I57" s="6"/>
       <c r="J57" s="2" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>13</v>
@@ -3230,7 +3239,7 @@
         <v>35</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>16</v>
@@ -3240,12 +3249,12 @@
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="2" t="s">
-        <v>199</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>200</v>
@@ -3254,10 +3263,10 @@
         <v>201</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>39</v>
@@ -3275,7 +3284,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>203</v>
@@ -3284,46 +3293,46 @@
         <v>204</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>205</v>
+        <v>16</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>16</v>
@@ -3335,7 +3344,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>210</v>
@@ -3344,13 +3353,13 @@
         <v>211</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>16</v>
@@ -3365,7 +3374,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>213</v>
@@ -3374,10 +3383,10 @@
         <v>214</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>21</v>
@@ -3395,7 +3404,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>216</v>
@@ -3404,13 +3413,13 @@
         <v>217</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>16</v>
@@ -3425,7 +3434,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>219</v>
@@ -3434,16 +3443,16 @@
         <v>220</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>16</v>
@@ -3455,7 +3464,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>222</v>
@@ -3464,16 +3473,16 @@
         <v>223</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>16</v>
@@ -3485,22 +3494,22 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>228</v>
+        <v>13</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>16</v>
@@ -3510,21 +3519,21 @@
       </c>
       <c r="I67" s="6"/>
       <c r="J67" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>14</v>
@@ -3540,21 +3549,21 @@
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="2" t="s">
-        <v>16</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>14</v>
@@ -3575,16 +3584,16 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>14</v>
@@ -3605,16 +3614,16 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>14</v>
@@ -3635,16 +3644,16 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>14</v>
@@ -3665,16 +3674,16 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>14</v>
@@ -3690,12 +3699,12 @@
       </c>
       <c r="I73" s="6"/>
       <c r="J73" s="2" t="s">
-        <v>242</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>243</v>
@@ -3704,7 +3713,7 @@
         <v>244</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>14</v>
@@ -3720,21 +3729,21 @@
       </c>
       <c r="I74" s="6"/>
       <c r="J74" s="2" t="s">
-        <v>16</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>14</v>
@@ -3755,16 +3764,16 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>14</v>
@@ -3780,12 +3789,12 @@
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="2" t="s">
-        <v>249</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>250</v>
@@ -3794,13 +3803,13 @@
         <v>251</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>16</v>
@@ -3815,7 +3824,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>253</v>
@@ -3824,13 +3833,13 @@
         <v>254</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>16</v>
@@ -3840,27 +3849,57 @@
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
         <v>255</v>
       </c>
     </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" s="6"/>
+      <c r="J79" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
-        <v>256</v>
+      <c r="A81" s="7" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="8" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J78"/>
-  <conditionalFormatting sqref="F2:F78">
+  <autoFilter ref="A1:J79"/>
+  <conditionalFormatting sqref="F2:F79">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"انجام شد"</formula>
     </cfRule>
@@ -3874,22 +3913,22 @@
       <formula>"به‌تعویق"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E78">
+  <conditionalFormatting sqref="E2:E79">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"بالا"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="E10:E78">
+    <dataValidation type="list" sqref="E10:E79">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E78">
+    <dataValidation type="list" sqref="E2:E79">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F10:F78">
+    <dataValidation type="list" sqref="F10:F79">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F78">
+    <dataValidation type="list" sqref="F2:F79">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3917,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
@@ -3926,16 +3965,16 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3943,60 +3982,60 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A2)</f>
-        <v>13</v>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A2)</f>
+        <v>14</v>
       </c>
       <c r="C2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
-        <v>7</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <v>8</v>
       </c>
       <c r="D2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A2,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>3</v>
       </c>
       <c r="H2" s="9">
         <f>IFERROR(C2/B2,0)</f>
-        <v>0.5384615384615384</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A3)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A3)</f>
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A3,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H3" s="9">
@@ -4006,30 +4045,30 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A4)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A4)</f>
         <v>8</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>7</v>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A4,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H4" s="9">
@@ -4039,30 +4078,30 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A5)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A5)</f>
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A5,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>8</v>
       </c>
       <c r="H5" s="9">
@@ -4072,30 +4111,30 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A6)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A6)</f>
         <v>11</v>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A6,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>6</v>
       </c>
       <c r="H6" s="9">
@@ -4105,30 +4144,30 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A7)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A7)</f>
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A7,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>5</v>
       </c>
       <c r="H7" s="9">
@@ -4138,30 +4177,30 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A8)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A8)</f>
         <v>14</v>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>5</v>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A8,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>4</v>
       </c>
       <c r="H8" s="9">
@@ -4171,30 +4210,30 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$78,A9)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A9)</f>
         <v>12</v>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
         <v>10</v>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$78,A9,'لیست کارها'!$F$2:$F$78,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
         <v>2</v>
       </c>
       <c r="H9" s="9">
@@ -4204,15 +4243,15 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B10" s="11">
         <f>SUM(B2:B9)</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D2:D9)</f>
@@ -4232,12 +4271,12 @@
       </c>
       <c r="H10" s="12">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0.4675324675324675</v>
+        <v>0.47435897435897434</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -4258,178 +4297,178 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4461,101 +4500,101 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/docs/OrganizationIntranet-ToDo.xlsx
+++ b/docs/OrganizationIntranet-ToDo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="328">
   <si>
     <t>فاز</t>
   </si>
@@ -607,7 +607,7 @@
     <t>افزودن تست برای هر فاز، به‌ویژه مرز عمومی/خصوصی (الان ۵۷ تست قبول است)</t>
   </si>
   <si>
-    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۶۶ تست قبول + ۱۲ تست بانک واقعی/نصب تازه (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
+    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۹۰ تست قبول + ۱۲ تست بانک واقعی/نصب تازه (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
   </si>
   <si>
     <t>P6-05</t>
@@ -679,7 +679,7 @@
     <t>صفحه‌های خطای ۴۰۴ و ۵۰۰ هم‌خوان با تم هر دو پرتال</t>
   </si>
   <si>
-    <t>الان صفحه‌ی Error پیش‌فرض است.</t>
+    <t>صفحه‌ی Error برای ۴۰۳/۴۰۴/۵۰۰ در هر پرتال (بدون وابستگی به API)، UseStatusCodePagesWithReExecute، مسیر AccessDenied هم‌تم. ErrorPagesTests.</t>
   </si>
   <si>
     <t>P6-13</t>
@@ -781,10 +781,19 @@
     <t>نمایش خطای ورود Portal به‌صورت توست تم پورتال</t>
   </si>
   <si>
-    <t>الان داخل کادر ورود نمایش داده می‌شود.</t>
+    <t>login-form.js اول portalToast را به کار می‌برد؛ پیام خروج هم توست؛ noscript پشتیبان.</t>
   </si>
   <si>
     <t>P7-12</t>
+  </si>
+  <si>
+    <t>رفع اسکرول افقی صفحه‌ی اصلی Portal در موبایل (پنل اعلان و منوی حساب)</t>
+  </si>
+  <si>
+    <t>پنل‌ها در عرض کمتر از ۹۶۰ fixed و وسط صفحه؛ قبلاً ۱۲۵ پیکسل سرریز.</t>
+  </si>
+  <si>
+    <t>P7-13</t>
   </si>
   <si>
     <t>جدول‌های پنل مدیریت در عرض موبایل (کارتی‌شدن ردیف‌ها یا اسکرول افقی بهتر)</t>
@@ -1496,7 +1505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3449,7 +3458,7 @@
         <v>35</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
@@ -3836,10 +3845,10 @@
         <v>231</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>16</v>
@@ -3866,10 +3875,10 @@
         <v>231</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>16</v>
@@ -3879,27 +3888,57 @@
       </c>
       <c r="I79" s="6"/>
       <c r="J79" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
         <v>258</v>
       </c>
     </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="6"/>
+      <c r="J80" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
-        <v>259</v>
+      <c r="A82" s="7" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="8" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J79"/>
-  <conditionalFormatting sqref="F2:F79">
+  <autoFilter ref="A1:J80"/>
+  <conditionalFormatting sqref="F2:F80">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"انجام شد"</formula>
     </cfRule>
@@ -3913,22 +3952,22 @@
       <formula>"به‌تعویق"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E79">
+  <conditionalFormatting sqref="E2:E80">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"بالا"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="E10:E79">
+    <dataValidation type="list" sqref="E10:E80">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E79">
+    <dataValidation type="list" sqref="E2:E80">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F10:F79">
+    <dataValidation type="list" sqref="F10:F80">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F79">
+    <dataValidation type="list" sqref="F2:F80">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3956,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
@@ -3965,7 +4004,7 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
@@ -3974,7 +4013,7 @@
         <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3982,27 +4021,27 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A2)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A2)</f>
         <v>14</v>
       </c>
       <c r="C2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>8</v>
       </c>
       <c r="D2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A2,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
         <v>3</v>
       </c>
       <c r="H2" s="9">
@@ -4015,27 +4054,27 @@
         <v>65</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A3)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A3)</f>
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A3,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H3" s="9">
@@ -4048,27 +4087,27 @@
         <v>79</v>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A4)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A4)</f>
         <v>8</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>7</v>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A4,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H4" s="9">
@@ -4081,27 +4120,27 @@
         <v>107</v>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A5)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A5)</f>
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A5,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
         <v>8</v>
       </c>
       <c r="H5" s="9">
@@ -4114,27 +4153,27 @@
         <v>135</v>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A6)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A6)</f>
         <v>11</v>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A6,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
         <v>6</v>
       </c>
       <c r="H6" s="9">
@@ -4147,27 +4186,27 @@
         <v>166</v>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A7)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A7)</f>
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A7,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
         <v>5</v>
       </c>
       <c r="H7" s="9">
@@ -4180,32 +4219,32 @@
         <v>185</v>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A8)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A8)</f>
         <v>14</v>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
-        <v>5</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <v>6</v>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A8,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
-        <v>4</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <v>3</v>
       </c>
       <c r="H8" s="9">
         <f>IFERROR(C8/B8,0)</f>
-        <v>0.35714285714285715</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -4213,45 +4252,45 @@
         <v>228</v>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$79,A9)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A9)</f>
+        <v>13</v>
+      </c>
+      <c r="C9" s="3">
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
         <v>12</v>
       </c>
-      <c r="C9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"انجام شد")</f>
-        <v>10</v>
-      </c>
       <c r="D9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$79,A9,'لیست کارها'!$F$2:$F$79,"انجام نشده")</f>
-        <v>2</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <v>1</v>
       </c>
       <c r="H9" s="9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.8333333333333334</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B10" s="11">
         <f>SUM(B2:B9)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D2:D9)</f>
@@ -4267,16 +4306,16 @@
       </c>
       <c r="G10" s="11">
         <f>SUM(G2:G9)</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" s="12">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0.47435897435897434</v>
+        <v>0.5063291139240507</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -4297,65 +4336,65 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>141</v>
@@ -4363,112 +4402,112 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4500,101 +4539,101 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/docs/OrganizationIntranet-ToDo.xlsx
+++ b/docs/OrganizationIntranet-ToDo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="332">
   <si>
     <t>فاز</t>
   </si>
@@ -607,7 +607,7 @@
     <t>افزودن تست برای هر فاز، به‌ویژه مرز عمومی/خصوصی (الان ۵۷ تست قبول است)</t>
   </si>
   <si>
-    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۹۰ تست قبول + ۱۲ تست بانک واقعی/نصب تازه (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
+    <t>قاعده‌ی «هر تغییر یک تست» برقرار است: ۱۹۷ تست قبول + ۱۲ تست بانک واقعی/نصب تازه (فقط‌خواندنی، اختیاری) قبول. ادامه‌دار برای هر تغییر.</t>
   </si>
   <si>
     <t>P6-05</t>
@@ -797,6 +797,18 @@
   </si>
   <si>
     <t>جدول‌های پنل مدیریت در عرض موبایل (کارتی‌شدن ردیف‌ها یا اسکرول افقی بهتر)</t>
+  </si>
+  <si>
+    <t>زیر ۷۶۸ پیکسل هر ردیف کارت با برچسب سرستون (admin-ui.js/css)؛ همه‌ی جدول‌های table-admin خودکار.</t>
+  </si>
+  <si>
+    <t>P7-14</t>
+  </si>
+  <si>
+    <t>صفحه‌ی «قوانین، انتشارات و فرم‌ها» (/Library) با تب بخش و جست‌وجو؛ یک دکمه‌ی «مشاهده‌ی همه» در صفحه‌ی اصلی</t>
+  </si>
+  <si>
+    <t>داده فعلاً ثابت (LibraryCatalog) تا اتصال به API فرم‌ها و اسناد در فاز ۳. LibraryTests.</t>
   </si>
   <si>
     <t>راهنما</t>
@@ -1505,7 +1517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3905,10 +3917,10 @@
         <v>231</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>16</v>
@@ -3918,27 +3930,57 @@
       </c>
       <c r="I80" s="6"/>
       <c r="J80" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
         <v>261</v>
       </c>
     </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="6"/>
+      <c r="J81" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
-        <v>262</v>
+      <c r="A83" s="7" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>263</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J80"/>
-  <conditionalFormatting sqref="F2:F80">
+  <autoFilter ref="A1:J81"/>
+  <conditionalFormatting sqref="F2:F81">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"انجام شد"</formula>
     </cfRule>
@@ -3952,22 +3994,22 @@
       <formula>"به‌تعویق"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E80">
+  <conditionalFormatting sqref="E2:E81">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"بالا"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="E10:E80">
+    <dataValidation type="list" sqref="E10:E81">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E80">
+    <dataValidation type="list" sqref="E2:E81">
       <formula1>"بالا,متوسط,پایین"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F10:F80">
+    <dataValidation type="list" sqref="F10:F81">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2:F80">
+    <dataValidation type="list" sqref="F2:F81">
       <formula1>"انجام نشده,در حال انجام,انجام شد,مسدود,به‌تعویق"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3995,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
@@ -4004,7 +4046,7 @@
         <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>21</v>
@@ -4013,7 +4055,7 @@
         <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4021,27 +4063,27 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A2)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A2)</f>
         <v>14</v>
       </c>
       <c r="C2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A2,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>8</v>
       </c>
       <c r="D2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A2,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A2,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A2,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G2" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A2,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A2,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>3</v>
       </c>
       <c r="H2" s="9">
@@ -4054,27 +4096,27 @@
         <v>65</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A3)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A3)</f>
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A3,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A3,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A3,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A3,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G3" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A3,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A3,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H3" s="9">
@@ -4087,27 +4129,27 @@
         <v>79</v>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A4)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A4)</f>
         <v>8</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A4,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>7</v>
       </c>
       <c r="D4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A4,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A4,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A4,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G4" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A4,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A4,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>1</v>
       </c>
       <c r="H4" s="9">
@@ -4120,27 +4162,27 @@
         <v>107</v>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A5)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A5)</f>
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A5,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>1</v>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A5,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A5,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A5,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A5,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A5,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>8</v>
       </c>
       <c r="H5" s="9">
@@ -4153,27 +4195,27 @@
         <v>135</v>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A6)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A6)</f>
         <v>11</v>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A6,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A6,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A6,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A6,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A6,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A6,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>6</v>
       </c>
       <c r="H6" s="9">
@@ -4186,27 +4228,27 @@
         <v>166</v>
       </c>
       <c r="B7" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A7)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A7)</f>
         <v>6</v>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A7,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A7,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A7,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A7,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A7,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A7,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>5</v>
       </c>
       <c r="H7" s="9">
@@ -4219,27 +4261,27 @@
         <v>185</v>
       </c>
       <c r="B8" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A8)</f>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A8)</f>
         <v>14</v>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A8,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
         <v>6</v>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A8,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A8,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A8,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>2</v>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A8,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A8,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
         <v>3</v>
       </c>
       <c r="H8" s="9">
@@ -4252,45 +4294,45 @@
         <v>228</v>
       </c>
       <c r="B9" s="3">
-        <f>COUNTIF('لیست کارها'!$A$2:$A$80,A9)</f>
-        <v>13</v>
+        <f>COUNTIF('لیست کارها'!$A$2:$A$81,A9)</f>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"انجام شد")</f>
-        <v>12</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A9,'لیست کارها'!$F$2:$F$81,"انجام شد")</f>
+        <v>14</v>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"در حال انجام")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A9,'لیست کارها'!$F$2:$F$81,"در حال انجام")</f>
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"مسدود")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A9,'لیست کارها'!$F$2:$F$81,"مسدود")</f>
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"به‌تعویق")</f>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A9,'لیست کارها'!$F$2:$F$81,"به‌تعویق")</f>
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS('لیست کارها'!$A$2:$A$80,A9,'لیست کارها'!$F$2:$F$80,"انجام نشده")</f>
-        <v>1</v>
+        <f>COUNTIFS('لیست کارها'!$A$2:$A$81,A9,'لیست کارها'!$F$2:$F$81,"انجام نشده")</f>
+        <v>0</v>
       </c>
       <c r="H9" s="9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.9230769230769231</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B10" s="11">
         <f>SUM(B2:B9)</f>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" s="11">
         <f>SUM(D2:D9)</f>
@@ -4306,16 +4348,16 @@
       </c>
       <c r="G10" s="11">
         <f>SUM(G2:G9)</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="12">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0.5063291139240507</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -4336,65 +4378,65 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>272</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>141</v>
@@ -4402,112 +4444,112 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -4539,101 +4581,101 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
